--- a/02_DIA_inicio_2026_analisis_assets/rbd_9433_escuela-basica-pablo-neruda_nt1_nucleos.xlsx
+++ b/02_DIA_inicio_2026_analisis_assets/rbd_9433_escuela-basica-pablo-neruda_nt1_nucleos.xlsx
@@ -775,13 +775,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EEEBA3AE-A25C-4464-AF4A-857387DA1AC1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{24A39F30-8954-4C06-B98C-20175D1E4C0A}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6F24A6E1-538F-49E0-9309-5731AAC74383}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5110A3A3-325B-407C-BC43-EEA787CE5F7D}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E258D85D-57EC-43C2-ABCA-EE1BAE3E0173}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4AFBB7D2-E238-4EBB-B737-3044D5C8C7F9}"/>
 </file>